--- a/tools/importer/reports/import-esg-environment.report.xlsx
+++ b/tools/importer/reports/import-esg-environment.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="70">
   <si>
     <t>_reportFile</t>
   </si>
@@ -43,12 +43,40 @@
     <t>viewportVariants</t>
   </si>
   <si>
+    <t>en/about-us/esg/environment.html.report.json</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Timeout 45000ms exceeded.
+Call log:
+  - navigating to "https://www.edc.ca/en/about-us/esg/environment.html", waiting until "domcontentloaded"
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">page.goto: Timeout 45000ms exceeded.
+Call log:
+  - navigating to "https://www.edc.ca/en/about-us/esg/environment.html", waiting until "domcontentloaded"
+    at processUrl (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:261:18)
+    at async main (/home/node/.excat-marketplace/excat/skills/excat-content-import/scripts/run-bulk-import.js:459:22)</t>
+  </si>
+  <si>
+    <t>en/about-us/esg/environment.html</t>
+  </si>
+  <si>
+    <t>failed</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-05-05T20:27:22.456Z</t>
+  </si>
+  <si>
+    <t>https://www.edc.ca/en/about-us/esg/environment.html</t>
+  </si>
+  <si>
     <t>en/about-us/esg/environment.report.json</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>en/about-us/esg/environment</t>
   </si>
   <si>
@@ -58,15 +86,12 @@
     <t>esg-environment</t>
   </si>
   <si>
-    <t>2026-05-04T22:13:03.281Z</t>
+    <t>2026-05-05T20:28:03.445Z</t>
   </si>
   <si>
     <t>Environment | EDC</t>
   </si>
   <si>
-    <t>https://www.edc.ca/en/about-us/esg/environment.html</t>
-  </si>
-  <si>
     <t>[{"alt":"Image of older women with tablet at an orchard representing sustainable responsible business and the environment.","desktop":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/environment-woman-vineyard-hero-d.jpg","tablet":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/environment-woman-vineyard-hero-t.jpg","mobile":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/environment-woman-vineyard-hero-m.jpg","fallback":"https://www.edc.ca/content/dam/edc/en/lifestyle/outdoor/environment-woman-vineyard-hero-m.jpg"}]</t>
   </si>
   <si>
@@ -76,7 +101,7 @@
     <t>en/about-us/esg/equator-principles</t>
   </si>
   <si>
-    <t>2026-05-04T23:14:07.445Z</t>
+    <t>2026-05-05T20:47:59.484Z</t>
   </si>
   <si>
     <t>Equator Principles | EDC</t>
@@ -91,7 +116,7 @@
     <t>en/about-us/esg/esg-governance</t>
   </si>
   <si>
-    <t>2026-05-04T22:13:20.336Z</t>
+    <t>2026-05-05T20:37:04.946Z</t>
   </si>
   <si>
     <t>ESG Governance | EDC</t>
@@ -109,7 +134,7 @@
     <t>en/about-us/esg/esg-metrics</t>
   </si>
   <si>
-    <t>2026-05-04T23:03:16.281Z</t>
+    <t>2026-05-05T20:43:05.678Z</t>
   </si>
   <si>
     <t>ESG metrics | EDC</t>
@@ -124,7 +149,7 @@
     <t>en/about-us/esg/risk-management</t>
   </si>
   <si>
-    <t>2026-05-04T23:03:09.464Z</t>
+    <t>2026-05-05T20:42:51.500Z</t>
   </si>
   <si>
     <t>Risk management | EDC</t>
@@ -151,9 +176,6 @@
     <t>en/about-us/esg/social.html</t>
   </si>
   <si>
-    <t>failed</t>
-  </si>
-  <si>
     <t>2026-05-04T20:16:51.854Z</t>
   </si>
   <si>
@@ -166,7 +188,7 @@
     <t>en/about-us/esg/social</t>
   </si>
   <si>
-    <t>2026-05-04T22:13:10.325Z</t>
+    <t>2026-05-05T20:37:54.776Z</t>
   </si>
   <si>
     <t>Social impact | EDC</t>
@@ -181,7 +203,7 @@
     <t>en/about-us/esg/sustainable-finance</t>
   </si>
   <si>
-    <t>2026-05-04T23:03:00.668Z</t>
+    <t>2026-05-05T20:42:59.636Z</t>
   </si>
   <si>
     <t>Sustainable finance | EDC</t>
@@ -600,7 +622,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="50" customWidth="1"/>
@@ -650,92 +672,92 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J3" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -743,19 +765,19 @@
         <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
         <v>32</v>
@@ -767,103 +789,103 @@
         <v>34</v>
       </c>
       <c r="J5" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
         <v>42</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>44</v>
       </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="I7" t="s">
         <v>45</v>
       </c>
-      <c r="H7" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
       <c r="J7" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" t="s">
         <v>47</v>
       </c>
-      <c r="B8" t="s">
-        <v>11</v>
-      </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="I8" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J8" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -871,19 +893,19 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
         <v>53</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G9" t="s">
         <v>54</v>
@@ -892,42 +914,74 @@
         <v>55</v>
       </c>
       <c r="I9" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
         <v>56</v>
-      </c>
-      <c r="J9" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G10" t="s">
         <v>59</v>
       </c>
-      <c r="E10" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="H10" t="s">
         <v>60</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>61</v>
       </c>
-      <c r="H10" t="s">
+      <c r="J10" t="s">
         <v>62</v>
       </c>
-      <c r="I10" t="s">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>63</v>
       </c>
-      <c r="J10" t="s">
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
         <v>64</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" t="s">
+        <v>67</v>
+      </c>
+      <c r="I11" t="s">
+        <v>68</v>
+      </c>
+      <c r="J11" t="s">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
